--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/网管服务器配置表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/网管服务器配置表.xlsx
@@ -450,8 +450,14 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -465,14 +471,8 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
